--- a/光伏配储项目/电价数据/2026/岐山站.xlsx
+++ b/光伏配储项目/电价数据/2026/岐山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.36024</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.83905</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.39137</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.41607</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.45502</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26511</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.42998</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.45888</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.40715</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.49166</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.19128</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.27687</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.26176</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.4933999999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>1.17397</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.62719</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.64138</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6018</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5842999999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.75325</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.16559</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.57352</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43723</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.67587</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9179400000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.53087</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.23371</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.38029</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.13164</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.1304</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.34134</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.44889</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.47282</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7315700000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.78553</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.23092</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.9621499999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.93138</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8160299999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7806900000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.52715</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4992</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47981</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4253</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43615</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.75291</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9321699999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.01223</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5274500000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5436599999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.53596</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53615</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.51646</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41507</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.49564</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.12122</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.08509</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.14554</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.48416</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.5770700000000001</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.57314</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.7835</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.74641</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9793099999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.45806</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.4090299999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.41364</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.51766</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.58841</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.51613</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.43298</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.44791</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.75013</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.4646</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.40885</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.03257</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6307200000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.81759</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.87967</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.23116</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.64067</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17283</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.90525</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.26492</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.15561</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.33973</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.08324</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.14017</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.69536</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.03483</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.94756</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.01969</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.89024</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.16148</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9694299999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.46114</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.9257300000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.97668</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45982</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43706</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.45386</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33621</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.53511</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.51181</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.51686</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.46525</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42916</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.44819</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.46687</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.41126</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.49963</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4576</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.45775</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.09426999999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.13505</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26451</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.45269</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.05251</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>1.15907</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.89124</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.87021</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1.14187</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.12591</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>1.04521</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.06883</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.03199</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>1.1046</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.9956699999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.9325800000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.11521</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5715399999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.67463</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8367899999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.89202</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.73322</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8185399999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5529299999999999</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.06991</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.4714</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45309</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.52785</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.53837</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.61653</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.67444</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.69814</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.7033200000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.38662</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6411399999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.69214</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47486</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50962</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.6856100000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.85211</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.83586</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.9754700000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48977</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.70662</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45745</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.54214</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.64813</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.87488</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.59876</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.9984299999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.7929700000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.65196</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.61015</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.74798</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44529</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46663</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34384</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.53967</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.51942</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45658</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46842</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42357</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44312</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.43501</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.5474600000000001</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.65888</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.43616</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.44932</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.26461</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.6395299999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.66535</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.58423</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.48402</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41736</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.46519</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.51607</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.7206</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.51112</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5510499999999999</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.48531</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40698</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.5133</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.63017</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.7371</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.5246499999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6502599999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.55938</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.47647</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45123</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.43504</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.34574</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13983</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.01774</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.6016</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.65318</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.6600900000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.45631</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.46153</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.16103</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.70374</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26335</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30464</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.43708</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40809</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.30865</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.24202</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.18872</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.20248</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.1894</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.26975</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.15561</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.11755</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.22162</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.14159</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.22745</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.15977</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27928</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.1365</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.22638</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.25039</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.16535</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.2547</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10051</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04219</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00915</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20456</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04844</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27299</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.12644</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00295</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05871</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05691</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31077</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.35266</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46484</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78615</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18706</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87012</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.64027</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5670599999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49313</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20697</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45422</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42149</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44188</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.54875</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5844600000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.90342</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.48111</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.25681</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.5574</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.27614</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8542000000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.28837</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.25706</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.61383</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.26599</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.17894</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.25394</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.14486</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.25026</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.24855</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.26524</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.24574</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.26994</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.27941</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28237</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.26857</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.31591</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.89095</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.27144</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.27925</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29196</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.27401</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.27862</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.28641</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.28668</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.21127</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.15271</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.18615</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.19376</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.24147</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20972</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.1878</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.27297</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44267</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.24503</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.21149</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.87218</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.56057</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.23181</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7227</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8322000000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.67152</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.15823</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.18313</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45363</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50889</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.45024</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.39735</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42474</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.25844</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.25778</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.40785</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.26055</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.26752</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.26395</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.26252</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.47492</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.13368</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.27479</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28687</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.26169</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14982</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27091</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28062</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02256</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28735</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.27023</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.27547</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.52647</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.27568</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.28546</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.26236</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.25135</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.24197</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.24317</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.23665</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.12455</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.15119</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.14958</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.14885</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.11407</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.22117</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.24371</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.24116</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.12139</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.12031</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.16541</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.13546</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.17703</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.15287</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.13696</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.22544</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.26244</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.11856</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.28421</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.1193</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.18853</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27975</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.1386</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25751</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27252</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.26441</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.27636</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.27596</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.26265</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.25528</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.28241</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.25768</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.26984</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.26894</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.27469</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.26756</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.25911</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.26421</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.26512</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.26528</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.26808</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.22422</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.26414</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.27684</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.25431</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.27018</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.27932</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.27885</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.27695</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.28251</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.26335</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.28466</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.28616</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.27827</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.26895</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.17793</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.24119</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.07626000000000001</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.07113</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.27971</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.09645000000000001</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.19657</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.1903</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.24656</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.1786</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.27236</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2737</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.25383</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.27295</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.29111</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.24428</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.26353</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.26618</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.27538</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.27925</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.28164</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.28366</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.16921</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41514</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.69053</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.49883</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.47188</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43898</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.50181</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42841</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.55972</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27379</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.21188</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7091499999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.45182</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.40363</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.54398</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43201</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.6476000000000001</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.46395</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46655</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.43743</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70436</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.16409</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.25338</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47345</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22134</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.25612</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.17397</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.25045</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.26808</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.26381</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.25572</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.16033</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.15403</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.25904</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.25981</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.25971</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.25979</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.15545</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.10865</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.21288</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.28542</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.24542</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.15293</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.15894</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.19217</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.16347</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.11869</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.11194</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.18098</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.21342</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.27835</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.26546</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.28559</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.24682</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.27806</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.28547</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.27577</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.26043</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.20317</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.28211</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.21015</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.27179</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.23798</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.26608</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.25046</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.26395</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.25747</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.26388</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.19479</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.12625</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31197</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28014</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.26273</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.25705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.27143</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.26057</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.28659</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.26847</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.26635</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.27184</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.25557</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.27407</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.26474</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.25989</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.26712</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28037</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.25887</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26041</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.62464</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.42771</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.1623</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.28417</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.26137</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.21865</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>-0.03707999999999999</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.10938</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.02021</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.12546</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.23436</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.19752</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.2695</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.22478</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.20444</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.19293</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.2636</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.39759</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.47395</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6543</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.61124</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.65522</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.26761</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8146</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.26657</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49551</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40523</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.27383</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.28985</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.30226</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.28815</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.28133</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.28814</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.25778</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.26735</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.23787</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.25724</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.22616</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.25882</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.26172</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.43589</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44144</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.4788</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.51571</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.55596</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42049</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67127</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40142</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.80989</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.19487</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.04617</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.05259</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.28554</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.26923</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.22249</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.18221</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.21816</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.22795</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.21986</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.74093</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.59116</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.63471</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.27472</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.27563</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.26983</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.28217</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.28158</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.21666</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.25783</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.26123</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.25061</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.26378</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.24676</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.25478</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.27178</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.19711</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.09747</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.29607</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.28775</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.19355</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.12576</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.19449</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.18853</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.21264</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.25239</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.25178</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.20512</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.24946</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.27673</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.13898</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.27789</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.13715</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.15079</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.14432</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.1859</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.15522</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.25764</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.23534</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.23796</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.19034</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.23335</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.17897</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.11841</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.23707</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.11874</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.16146</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.11744</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.11034</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.11378</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.15785</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.11202</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.11413</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.11623</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.11834</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.12679</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.14594</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.10451</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.27549</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>-0.01943</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.16993</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.01076</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.22372</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.23289</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.25251</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.04108</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.04977</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.27347</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.21969</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.24582</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.27052</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28082</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.23539</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.26412</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.24835</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.24521</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.17829</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.20796</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.18577</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.21045</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.24084</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.23271</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.22486</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.12914</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.13516</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.23228</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.12074</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.26137</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.12298</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.21026</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.20426</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.26612</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.26633</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.26273</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.25527</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-0.03664</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.14523</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.25651</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.18073</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.20498</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.19555</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.02396</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.17514</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.14909</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.23874</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.01852</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.01226</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.16378</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02216</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01321</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04090999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04862</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02938</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00466</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03486</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.00551</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03482</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.2115</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27174</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27974</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28995</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27363</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28722</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28133</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28137</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.25324</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.23839</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.24556</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.27689</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.24937</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.24931</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.25851</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.13064</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.12794</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.13167</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.12615</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.11694</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.40917</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.15186</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26008</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.20253</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.18033</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85237</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86365</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08279</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.23556</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28049</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.41124</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.70677</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00315</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.07049</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25451</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47612</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.52095</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.48194</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.28217</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.70533</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.95365</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.57573</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8138</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8120299999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.81628</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9141699999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.28633</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.29388</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.27388</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.25563</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.46535</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.26835</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.26301</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.24038</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.14994</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.24071</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.23321</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.22758</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.18932</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.20574</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.17253</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.13016</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.16861</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.12559</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.12787</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.11192</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.14246</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.19873</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.23559</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.2106</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.21787</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29196</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.23544</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26198</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.27463</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.26173</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25887</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.28722</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.21391</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.27708</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.28267</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.27748</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27399</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.27258</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.54789</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.25284</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45314</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.42229</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47581</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.04391</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.81713</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.78834</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.39746</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.53647</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6289199999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.86564</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5221</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41487</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19057</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.30575</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.28713</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.28886</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43452</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50739</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.49894</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.03949</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.79418</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.52234</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.67101</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46438</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.55243</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49101</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.41997</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6494800000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.60527</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8322000000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.70728</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.56221</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31042</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27883</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.27669</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.2699</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.27405</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.26443</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5088199999999999</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19682</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43471</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.47248</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.28599</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.49616</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.44186</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.52946</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43254</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42115</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.53531</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47034</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.40831</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.31355</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.66587</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.4411600000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.25083</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.46969</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.46561</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.47887</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.46147</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.49185</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41208</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.49564</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.40792</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44351</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33072</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17622</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14587</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19882</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14824</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12242</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22729</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14637</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18604</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22702</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27737</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16255</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.17369</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20559</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.16377</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.46352</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.40462</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.60781</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.42427</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.43967</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.4517</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40509</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.49831</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.45543</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.50534</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.49036</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.46657</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.45791</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4813</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41002</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36317</v>
       </c>
     </row>
   </sheetData>
